--- a/paper_result_final/paper_results_tables/All_Tables_Main_and_Apppendix.xlsx
+++ b/paper_result_final/paper_results_tables/All_Tables_Main_and_Apppendix.xlsx
@@ -552,7 +552,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>KFold then supplier-held-out GroupKFold</t>
+          <t>KFold then supplier-held-out Group KFold</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -594,12 +594,12 @@
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="21" customWidth="1" min="3" max="3"/>
-    <col width="24" customWidth="1" min="4" max="4"/>
-    <col width="23" customWidth="1" min="5" max="5"/>
-    <col width="23" customWidth="1" min="6" max="6"/>
-    <col width="20" customWidth="1" min="7" max="7"/>
-    <col width="20" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="17" customWidth="1" min="4" max="4"/>
+    <col width="19" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -650,26 +650,40 @@
           <t>KFold</t>
         </is>
       </c>
-      <c r="B2" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C2" s="2" t="n">
-        <v>0.07378124583338641</v>
-      </c>
-      <c r="D2" s="2" t="n">
-        <v>-0.005837735044462904</v>
-      </c>
-      <c r="E2" s="2" t="n">
-        <v>-0.007156111974827795</v>
-      </c>
-      <c r="F2" s="2" t="n">
-        <v>0.001883402204273271</v>
-      </c>
-      <c r="G2" s="2" t="n">
-        <v>0.8333990960862956</v>
-      </c>
-      <c r="H2" s="2" t="n">
-        <v>3.347222222222222</v>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>0.074</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>-0.006</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>-0.007</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>0.002</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>0.833</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>3.347</t>
+        </is>
       </c>
     </row>
     <row r="3">
@@ -678,26 +692,40 @@
           <t>KFold</t>
         </is>
       </c>
-      <c r="B3" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="C3" s="2" t="n">
-        <v>0.2147854557518087</v>
-      </c>
-      <c r="D3" s="2" t="n">
-        <v>-0.01367546125134336</v>
-      </c>
-      <c r="E3" s="2" t="n">
-        <v>-0.01669906050491266</v>
-      </c>
-      <c r="F3" s="2" t="n">
-        <v>0.007701180717144356</v>
-      </c>
-      <c r="G3" s="2" t="n">
-        <v>0.8477947995440442</v>
-      </c>
-      <c r="H3" s="2" t="n">
-        <v>3.552083333333333</v>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>0.215</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>-0.014</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>-0.017</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>0.008</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>0.848</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>3.552</t>
+        </is>
       </c>
     </row>
     <row r="4">
@@ -706,26 +734,40 @@
           <t>KFold</t>
         </is>
       </c>
-      <c r="B4" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="C4" s="2" t="n">
-        <v>0.3749678977850497</v>
-      </c>
-      <c r="D4" s="2" t="n">
-        <v>-0.01658810909981084</v>
-      </c>
-      <c r="E4" s="2" t="n">
-        <v>-0.02562161517626649</v>
-      </c>
-      <c r="F4" s="2" t="n">
-        <v>0.02232126244974927</v>
-      </c>
-      <c r="G4" s="2" t="n">
-        <v>0.8473396400432163</v>
-      </c>
-      <c r="H4" s="2" t="n">
-        <v>3.614583333333333</v>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>0.375</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>-0.017</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>-0.026</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>0.022</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0.847</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>3.615</t>
+        </is>
       </c>
     </row>
     <row r="5">
@@ -734,26 +776,40 @@
           <t>KFold</t>
         </is>
       </c>
-      <c r="B5" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="C5" s="2" t="n">
-        <v>0.5495485829887734</v>
-      </c>
-      <c r="D5" s="2" t="n">
-        <v>-0.03434261967375685</v>
-      </c>
-      <c r="E5" s="2" t="n">
-        <v>-0.04377201935588593</v>
-      </c>
-      <c r="F5" s="2" t="n">
-        <v>0.03549834013441752</v>
-      </c>
-      <c r="G5" s="2" t="n">
-        <v>0.8350830162087505</v>
-      </c>
-      <c r="H5" s="2" t="n">
-        <v>3.420138888888889</v>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>0.550</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>-0.034</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>-0.044</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>0.035</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>0.835</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>3.420</t>
+        </is>
       </c>
     </row>
     <row r="6">
@@ -762,26 +818,40 @@
           <t>KFold</t>
         </is>
       </c>
-      <c r="B6" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="C6" s="2" t="n">
-        <v>0.7342238846350062</v>
-      </c>
-      <c r="D6" s="2" t="n">
-        <v>-0.01643639091037694</v>
-      </c>
-      <c r="E6" s="2" t="n">
-        <v>-0.04947994930342148</v>
-      </c>
-      <c r="F6" s="2" t="n">
-        <v>0.06769268754632038</v>
-      </c>
-      <c r="G6" s="2" t="n">
-        <v>0.8386700627654426</v>
-      </c>
-      <c r="H6" s="2" t="n">
-        <v>3.392361111111111</v>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>0.734</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>-0.016</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>-0.049</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>0.068</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>0.839</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>3.392</t>
+        </is>
       </c>
     </row>
     <row r="7">
@@ -790,26 +860,40 @@
           <t>KFold</t>
         </is>
       </c>
-      <c r="B7" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="C7" s="2" t="n">
-        <v>0.9593725226743723</v>
-      </c>
-      <c r="D7" s="2" t="n">
-        <v>-0.04854896919551971</v>
-      </c>
-      <c r="E7" s="2" t="n">
-        <v>-0.07198638150744152</v>
-      </c>
-      <c r="F7" s="2" t="n">
-        <v>0.07447254520292118</v>
-      </c>
-      <c r="G7" s="2" t="n">
-        <v>0.8320587493558264</v>
-      </c>
-      <c r="H7" s="2" t="n">
-        <v>3.372822299651568</v>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>0.959</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>-0.049</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>-0.072</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>0.074</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>0.832</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>3.373</t>
+        </is>
       </c>
     </row>
     <row r="8">
@@ -818,26 +902,40 @@
           <t>KFold</t>
         </is>
       </c>
-      <c r="B8" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="C8" s="2" t="n">
-        <v>1.24822144914136</v>
-      </c>
-      <c r="D8" s="2" t="n">
-        <v>-0.003272874220759725</v>
-      </c>
-      <c r="E8" s="2" t="n">
-        <v>-0.01662025300975656</v>
-      </c>
-      <c r="F8" s="2" t="n">
-        <v>0.1204736472423475</v>
-      </c>
-      <c r="G8" s="2" t="n">
-        <v>0.831430635451339</v>
-      </c>
-      <c r="H8" s="2" t="n">
-        <v>3.295138888888889</v>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>1.248</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>-0.003</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>-0.017</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>0.120</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>0.831</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>3.295</t>
+        </is>
       </c>
     </row>
     <row r="9">
@@ -846,26 +944,40 @@
           <t>KFold</t>
         </is>
       </c>
-      <c r="B9" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="C9" s="2" t="n">
-        <v>1.617647041763374</v>
-      </c>
-      <c r="D9" s="2" t="n">
-        <v>-0.01118584318582089</v>
-      </c>
-      <c r="E9" s="2" t="n">
-        <v>-0.06874258895723173</v>
-      </c>
-      <c r="F9" s="2" t="n">
-        <v>0.2136446180176423</v>
-      </c>
-      <c r="G9" s="2" t="n">
-        <v>0.8242188118906355</v>
-      </c>
-      <c r="H9" s="2" t="n">
-        <v>3.15625</v>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>1.618</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>-0.011</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>-0.069</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>0.214</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>0.824</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>3.156</t>
+        </is>
       </c>
     </row>
     <row r="10">
@@ -874,26 +986,40 @@
           <t>KFold</t>
         </is>
       </c>
-      <c r="B10" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="C10" s="2" t="n">
-        <v>2.134249000517736</v>
-      </c>
-      <c r="D10" s="2" t="n">
-        <v>-0.02277153536900062</v>
-      </c>
-      <c r="E10" s="2" t="n">
-        <v>-0.1077133316310865</v>
-      </c>
-      <c r="F10" s="2" t="n">
-        <v>0.137571225397226</v>
-      </c>
-      <c r="G10" s="2" t="n">
-        <v>0.8087436940747066</v>
-      </c>
-      <c r="H10" s="2" t="n">
-        <v>2.885416666666667</v>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>2.134</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>-0.023</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>-0.108</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>0.138</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>0.809</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>2.885</t>
+        </is>
       </c>
     </row>
     <row r="11">
@@ -902,26 +1028,40 @@
           <t>KFold</t>
         </is>
       </c>
-      <c r="B11" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="C11" s="2" t="n">
-        <v>3.352477996329129</v>
-      </c>
-      <c r="D11" s="2" t="n">
-        <v>0.007360192478544803</v>
-      </c>
-      <c r="E11" s="2" t="n">
-        <v>0.2272947645081946</v>
-      </c>
-      <c r="F11" s="2" t="n">
-        <v>0.3797431789771481</v>
-      </c>
-      <c r="G11" s="2" t="n">
-        <v>0.7839622821779784</v>
-      </c>
-      <c r="H11" s="2" t="n">
-        <v>2.489583333333333</v>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>3.352</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>0.007</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>0.227</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>0.380</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>0.784</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>2.490</t>
+        </is>
       </c>
     </row>
     <row r="12">
@@ -930,26 +1070,40 @@
           <t>Group KFold</t>
         </is>
       </c>
-      <c r="B12" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C12" s="2" t="n">
-        <v>0.1781721112097616</v>
-      </c>
-      <c r="D12" s="2" t="n">
-        <v>-0.002099204975671065</v>
-      </c>
-      <c r="E12" s="2" t="n">
-        <v>-0.01081539162043876</v>
-      </c>
-      <c r="F12" s="2" t="n">
-        <v>0.00657464434351604</v>
-      </c>
-      <c r="G12" s="2" t="n">
-        <v>0.879463863263697</v>
-      </c>
-      <c r="H12" s="2" t="n">
-        <v>4.333333333333333</v>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>0.178</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>-0.002</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>-0.011</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>0.007</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>0.879</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>4.333</t>
+        </is>
       </c>
     </row>
     <row r="13">
@@ -958,26 +1112,40 @@
           <t>Group KFold</t>
         </is>
       </c>
-      <c r="B13" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="C13" s="2" t="n">
-        <v>0.5387509135317117</v>
-      </c>
-      <c r="D13" s="2" t="n">
-        <v>-0.003449783763194547</v>
-      </c>
-      <c r="E13" s="2" t="n">
-        <v>-0.01956880189503751</v>
-      </c>
-      <c r="F13" s="2" t="n">
-        <v>0.02533947546744296</v>
-      </c>
-      <c r="G13" s="2" t="n">
-        <v>0.8900037637446457</v>
-      </c>
-      <c r="H13" s="2" t="n">
-        <v>4.479166666666667</v>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>0.539</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>-0.003</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>-0.020</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>0.025</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>0.890</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>4.479</t>
+        </is>
       </c>
     </row>
     <row r="14">
@@ -986,26 +1154,40 @@
           <t>Group KFold</t>
         </is>
       </c>
-      <c r="B14" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="C14" s="2" t="n">
-        <v>0.8707707029608089</v>
-      </c>
-      <c r="D14" s="2" t="n">
-        <v>-0.007940734211526357</v>
-      </c>
-      <c r="E14" s="2" t="n">
-        <v>-0.05843600801970128</v>
-      </c>
-      <c r="F14" s="2" t="n">
-        <v>0.04442537704387828</v>
-      </c>
-      <c r="G14" s="2" t="n">
-        <v>0.874726030862064</v>
-      </c>
-      <c r="H14" s="2" t="n">
-        <v>4.194444444444445</v>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>0.871</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>-0.008</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>-0.058</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>0.044</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>0.875</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>4.194</t>
+        </is>
       </c>
     </row>
     <row r="15">
@@ -1014,26 +1196,40 @@
           <t>Group KFold</t>
         </is>
       </c>
-      <c r="B15" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="C15" s="2" t="n">
-        <v>1.249033197853505</v>
-      </c>
-      <c r="D15" s="2" t="n">
-        <v>-0.01739822537858615</v>
-      </c>
-      <c r="E15" s="2" t="n">
-        <v>-0.09097224680931904</v>
-      </c>
-      <c r="F15" s="2" t="n">
-        <v>0.04419092503853093</v>
-      </c>
-      <c r="G15" s="2" t="n">
-        <v>0.8888095163083692</v>
-      </c>
-      <c r="H15" s="2" t="n">
-        <v>4.434027777777778</v>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>1.249</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>-0.017</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>-0.091</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>0.044</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>0.889</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>4.434</t>
+        </is>
       </c>
     </row>
     <row r="16">
@@ -1042,26 +1238,40 @@
           <t>Group KFold</t>
         </is>
       </c>
-      <c r="B16" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="C16" s="2" t="n">
-        <v>1.55821103353496</v>
-      </c>
-      <c r="D16" s="2" t="n">
-        <v>-0.01811023148492263</v>
-      </c>
-      <c r="E16" s="2" t="n">
-        <v>-0.1051949950315998</v>
-      </c>
-      <c r="F16" s="2" t="n">
-        <v>0.172580439899787</v>
-      </c>
-      <c r="G16" s="2" t="n">
-        <v>0.8895495295866193</v>
-      </c>
-      <c r="H16" s="2" t="n">
-        <v>4.517361111111111</v>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>1.558</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>-0.018</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>-0.105</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>0.173</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>0.890</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>4.517</t>
+        </is>
       </c>
     </row>
     <row r="17">
@@ -1070,26 +1280,40 @@
           <t>Group KFold</t>
         </is>
       </c>
-      <c r="B17" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="C17" s="2" t="n">
-        <v>1.900039133866679</v>
-      </c>
-      <c r="D17" s="2" t="n">
-        <v>-0.001796738588002222</v>
-      </c>
-      <c r="E17" s="2" t="n">
-        <v>-0.05215370742218184</v>
-      </c>
-      <c r="F17" s="2" t="n">
-        <v>0.4337707907443356</v>
-      </c>
-      <c r="G17" s="2" t="n">
-        <v>0.8861269906147097</v>
-      </c>
-      <c r="H17" s="2" t="n">
-        <v>4.428571428571429</v>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>1.900</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>-0.002</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>-0.052</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>0.434</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>0.886</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>4.429</t>
+        </is>
       </c>
     </row>
     <row r="18">
@@ -1098,26 +1322,40 @@
           <t>Group KFold</t>
         </is>
       </c>
-      <c r="B18" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="C18" s="2" t="n">
-        <v>2.246906250862445</v>
-      </c>
-      <c r="D18" s="2" t="n">
-        <v>-0.01025216814025826</v>
-      </c>
-      <c r="E18" s="2" t="n">
-        <v>-0.08780302539047424</v>
-      </c>
-      <c r="F18" s="2" t="n">
-        <v>0.3009979166843777</v>
-      </c>
-      <c r="G18" s="2" t="n">
-        <v>0.8928526820462211</v>
-      </c>
-      <c r="H18" s="2" t="n">
-        <v>4.572916666666667</v>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>2.247</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>-0.010</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>-0.088</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>0.301</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>0.893</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>4.573</t>
+        </is>
       </c>
     </row>
     <row r="19">
@@ -1126,26 +1364,40 @@
           <t>Group KFold</t>
         </is>
       </c>
-      <c r="B19" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="C19" s="2" t="n">
-        <v>2.633251281425144</v>
-      </c>
-      <c r="D19" s="2" t="n">
-        <v>-0.02437751849569642</v>
-      </c>
-      <c r="E19" s="2" t="n">
-        <v>-0.1934037655001482</v>
-      </c>
-      <c r="F19" s="2" t="n">
-        <v>0.4304206978475902</v>
-      </c>
-      <c r="G19" s="2" t="n">
-        <v>0.8880990691136422</v>
-      </c>
-      <c r="H19" s="2" t="n">
-        <v>4.493055555555555</v>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>2.633</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>-0.024</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>-0.193</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>0.430</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>0.888</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>4.493</t>
+        </is>
       </c>
     </row>
     <row r="20">
@@ -1154,26 +1406,40 @@
           <t>Group KFold</t>
         </is>
       </c>
-      <c r="B20" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="C20" s="2" t="n">
-        <v>3.094149292273969</v>
-      </c>
-      <c r="D20" s="2" t="n">
-        <v>0.191694691031887</v>
-      </c>
-      <c r="E20" s="2" t="n">
-        <v>0.2166614920090995</v>
-      </c>
-      <c r="F20" s="2" t="n">
-        <v>0.7738696313294557</v>
-      </c>
-      <c r="G20" s="2" t="n">
-        <v>0.8856239637540424</v>
-      </c>
-      <c r="H20" s="2" t="n">
-        <v>4.409722222222222</v>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>3.094</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>0.192</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>0.217</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>0.774</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>0.886</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>4.410</t>
+        </is>
       </c>
     </row>
     <row r="21">
@@ -1182,26 +1448,40 @@
           <t>Group KFold</t>
         </is>
       </c>
-      <c r="B21" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="C21" s="2" t="n">
-        <v>4.030175502556355</v>
-      </c>
-      <c r="D21" s="2" t="n">
-        <v>0.4174535851466159</v>
-      </c>
-      <c r="E21" s="2" t="n">
-        <v>0.3019767607879407</v>
-      </c>
-      <c r="F21" s="2" t="n">
-        <v>1.360731827487278</v>
-      </c>
-      <c r="G21" s="2" t="n">
-        <v>0.8555811902269966</v>
-      </c>
-      <c r="H21" s="2" t="n">
-        <v>3.885416666666667</v>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>4.030</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>0.417</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>0.302</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>1.361</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>0.856</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>3.885</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -1301,8 +1581,16 @@
           <t>0.973 (0.033)</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr"/>
-      <c r="H2" s="2" t="inlineStr"/>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1335,8 +1623,16 @@
           <t>0.819 (0.057)</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr"/>
-      <c r="H3" s="2" t="inlineStr"/>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1369,8 +1665,16 @@
           <t>0.799 (0.083)</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr"/>
-      <c r="H4" s="2" t="inlineStr"/>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1408,8 +1712,10 @@
           <t>81.31%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="n">
-        <v>4.381</v>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>4.381</t>
+        </is>
       </c>
     </row>
     <row r="6">
@@ -1448,8 +1754,10 @@
           <t>81.94%</t>
         </is>
       </c>
-      <c r="H6" s="2" t="n">
-        <v>4.438</v>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>4.438</t>
+        </is>
       </c>
     </row>
     <row r="7">
@@ -1483,8 +1791,16 @@
           <t>0.974 (0.041)</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr"/>
-      <c r="H7" s="2" t="inlineStr"/>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -1517,8 +1833,16 @@
           <t>0.816 (0.033)</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr"/>
-      <c r="H8" s="2" t="inlineStr"/>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -1551,8 +1875,16 @@
           <t>0.757 (0.139)</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr"/>
-      <c r="H9" s="2" t="inlineStr"/>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -1590,8 +1922,10 @@
           <t>83.64%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="n">
-        <v>5.169</v>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>5.169</t>
+        </is>
       </c>
     </row>
     <row r="11">
@@ -1630,8 +1964,10 @@
           <t>85.00%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="n">
-        <v>5.328</v>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>5.328</t>
+        </is>
       </c>
     </row>
     <row r="12">
@@ -1665,8 +2001,16 @@
           <t>0.930 (0.023)</t>
         </is>
       </c>
-      <c r="G12" s="2" t="inlineStr"/>
-      <c r="H12" s="2" t="inlineStr"/>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -1699,8 +2043,16 @@
           <t>0.808 (0.070)</t>
         </is>
       </c>
-      <c r="G13" s="2" t="inlineStr"/>
-      <c r="H13" s="2" t="inlineStr"/>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -1733,8 +2085,16 @@
           <t>0.712 (0.148)</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr"/>
-      <c r="H14" s="2" t="inlineStr"/>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -1772,8 +2132,10 @@
           <t>82.04%</t>
         </is>
       </c>
-      <c r="H15" s="2" t="n">
-        <v>4.381</v>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>4.381</t>
+        </is>
       </c>
     </row>
     <row r="16">
@@ -1812,8 +2174,10 @@
           <t>84.75%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="n">
-        <v>4.694</v>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>4.694</t>
+        </is>
       </c>
     </row>
     <row r="17">
@@ -1847,8 +2211,16 @@
           <t>0.950 (0.046)</t>
         </is>
       </c>
-      <c r="G17" s="2" t="inlineStr"/>
-      <c r="H17" s="2" t="inlineStr"/>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -1881,8 +2253,16 @@
           <t>0.964 (0.119)</t>
         </is>
       </c>
-      <c r="G18" s="2" t="inlineStr"/>
-      <c r="H18" s="2" t="inlineStr"/>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -1915,8 +2295,16 @@
           <t>0.979 (0.124)</t>
         </is>
       </c>
-      <c r="G19" s="2" t="inlineStr"/>
-      <c r="H19" s="2" t="inlineStr"/>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -1954,8 +2342,10 @@
           <t>72.66%</t>
         </is>
       </c>
-      <c r="H20" s="2" t="n">
-        <v>4.381</v>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>4.381</t>
+        </is>
       </c>
     </row>
     <row r="21">
@@ -1994,8 +2384,10 @@
           <t>73.67%</t>
         </is>
       </c>
-      <c r="H21" s="2" t="n">
-        <v>4.453</v>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>4.453</t>
+        </is>
       </c>
     </row>
     <row r="22">
@@ -2029,8 +2421,16 @@
           <t>1.020 (0.067)</t>
         </is>
       </c>
-      <c r="G22" s="2" t="inlineStr"/>
-      <c r="H22" s="2" t="inlineStr"/>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -2063,8 +2463,16 @@
           <t>1.005 (0.095)</t>
         </is>
       </c>
-      <c r="G23" s="2" t="inlineStr"/>
-      <c r="H23" s="2" t="inlineStr"/>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -2097,8 +2505,16 @@
           <t>0.983 (0.047)</t>
         </is>
       </c>
-      <c r="G24" s="2" t="inlineStr"/>
-      <c r="H24" s="2" t="inlineStr"/>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -2136,8 +2552,10 @@
           <t>70.02%</t>
         </is>
       </c>
-      <c r="H25" s="2" t="n">
-        <v>4.658</v>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>4.658</t>
+        </is>
       </c>
     </row>
     <row r="26">
@@ -2176,8 +2594,10 @@
           <t>68.91%</t>
         </is>
       </c>
-      <c r="H26" s="2" t="n">
-        <v>4.739</v>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>4.739</t>
+        </is>
       </c>
     </row>
     <row r="27">
@@ -2211,8 +2631,16 @@
           <t>0.992 (0.029)</t>
         </is>
       </c>
-      <c r="G27" s="2" t="inlineStr"/>
-      <c r="H27" s="2" t="inlineStr"/>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -2245,8 +2673,16 @@
           <t>0.939 (0.039)</t>
         </is>
       </c>
-      <c r="G28" s="2" t="inlineStr"/>
-      <c r="H28" s="2" t="inlineStr"/>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -2279,8 +2715,16 @@
           <t>1.361 (0.771)</t>
         </is>
       </c>
-      <c r="G29" s="2" t="inlineStr"/>
-      <c r="H29" s="2" t="inlineStr"/>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -2318,8 +2762,10 @@
           <t>74.23%</t>
         </is>
       </c>
-      <c r="H30" s="2" t="n">
-        <v>4.381</v>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>4.381</t>
+        </is>
       </c>
     </row>
     <row r="31">
@@ -2358,8 +2804,10 @@
           <t>73.81%</t>
         </is>
       </c>
-      <c r="H31" s="2" t="n">
-        <v>4.494</v>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>4.494</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -2448,8 +2896,16 @@
           <t>0.930 (0.023)</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr"/>
-      <c r="G2" s="2" t="inlineStr"/>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -2477,8 +2933,16 @@
           <t>0.808 (0.070)</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr"/>
-      <c r="G3" s="2" t="inlineStr"/>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -2506,8 +2970,16 @@
           <t>0.712 (0.148)</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr"/>
-      <c r="G4" s="2" t="inlineStr"/>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -2540,8 +3012,10 @@
           <t>94.93%</t>
         </is>
       </c>
-      <c r="G5" s="2" t="n">
-        <v>7.749</v>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>7.749</t>
+        </is>
       </c>
     </row>
     <row r="6">
@@ -2575,8 +3049,10 @@
           <t>94.82%</t>
         </is>
       </c>
-      <c r="G6" s="2" t="n">
-        <v>7.755</v>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>7.755</t>
+        </is>
       </c>
     </row>
     <row r="7">
@@ -2610,8 +3086,10 @@
           <t>82.04%</t>
         </is>
       </c>
-      <c r="G7" s="2" t="n">
-        <v>4.381</v>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>4.381</t>
+        </is>
       </c>
     </row>
     <row r="8">
@@ -2645,8 +3123,10 @@
           <t>84.75%</t>
         </is>
       </c>
-      <c r="G8" s="2" t="n">
-        <v>4.694</v>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>4.694</t>
+        </is>
       </c>
     </row>
     <row r="9">
@@ -2675,8 +3155,16 @@
           <t>0.992 (0.029)</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr"/>
-      <c r="G9" s="2" t="inlineStr"/>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -2704,8 +3192,16 @@
           <t>0.939 (0.039)</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr"/>
-      <c r="G10" s="2" t="inlineStr"/>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2733,8 +3229,16 @@
           <t>1.361 (0.771)</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr"/>
-      <c r="G11" s="2" t="inlineStr"/>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -2767,8 +3271,10 @@
           <t>95.21%</t>
         </is>
       </c>
-      <c r="G12" s="2" t="n">
-        <v>11.214</v>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>11.214</t>
+        </is>
       </c>
     </row>
     <row r="13">
@@ -2802,8 +3308,10 @@
           <t>92.53%</t>
         </is>
       </c>
-      <c r="G13" s="2" t="n">
-        <v>10.426</v>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>10.426</t>
+        </is>
       </c>
     </row>
     <row r="14">
@@ -2837,8 +3345,10 @@
           <t>74.23%</t>
         </is>
       </c>
-      <c r="G14" s="2" t="n">
-        <v>4.381</v>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>4.381</t>
+        </is>
       </c>
     </row>
     <row r="15">
@@ -2872,8 +3382,10 @@
           <t>73.81%</t>
         </is>
       </c>
-      <c r="G15" s="2" t="n">
-        <v>4.494</v>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>4.494</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -2893,7 +3405,7 @@
     <col width="13" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
     <col width="33" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
     <col width="21" customWidth="1" min="5" max="5"/>
     <col width="21" customWidth="1" min="6" max="6"/>
   </cols>
@@ -2936,20 +3448,30 @@
           <t>KFold</t>
         </is>
       </c>
-      <c r="B2" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C2" s="2" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="D2" s="2" t="n">
-        <v>1.920928210219043</v>
-      </c>
-      <c r="E2" s="2" t="n">
-        <v>3.970669502979073</v>
-      </c>
-      <c r="F2" s="2" t="n">
-        <v>3.976621676810158</v>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>0.55</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>1.921</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>3.971</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>3.977</t>
+        </is>
       </c>
     </row>
     <row r="3">
@@ -2958,20 +3480,30 @@
           <t>KFold</t>
         </is>
       </c>
-      <c r="B3" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="C3" s="2" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="D3" s="2" t="n">
-        <v>1.988099049584731</v>
-      </c>
-      <c r="E3" s="2" t="n">
-        <v>4.464181895940524</v>
-      </c>
-      <c r="F3" s="2" t="n">
-        <v>4.478958317731783</v>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>0.75</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>1.988</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>4.464</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>4.479</t>
+        </is>
       </c>
     </row>
     <row r="4">
@@ -2980,20 +3512,30 @@
           <t>KFold</t>
         </is>
       </c>
-      <c r="B4" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="C4" s="2" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="D4" s="2" t="n">
-        <v>1.815222386226918</v>
-      </c>
-      <c r="E4" s="2" t="n">
-        <v>3.769296831616805</v>
-      </c>
-      <c r="F4" s="2" t="n">
-        <v>3.693052385547382</v>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>0.45</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>1.815</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>3.769</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>3.693</t>
+        </is>
       </c>
     </row>
     <row r="5">
@@ -3002,20 +3544,30 @@
           <t>KFold</t>
         </is>
       </c>
-      <c r="B5" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="C5" s="2" t="n">
-        <v>0.6000000000000001</v>
-      </c>
-      <c r="D5" s="2" t="n">
-        <v>1.62721289620914</v>
-      </c>
-      <c r="E5" s="2" t="n">
-        <v>3.538479555729712</v>
-      </c>
-      <c r="F5" s="2" t="n">
-        <v>3.595841591143798</v>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>0.60</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>1.627</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>3.538</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>3.596</t>
+        </is>
       </c>
     </row>
     <row r="6">
@@ -3024,130 +3576,190 @@
           <t>KFold</t>
         </is>
       </c>
-      <c r="B6" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="C6" s="2" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="D6" s="2" t="n">
-        <v>1.582905706002324</v>
-      </c>
-      <c r="E6" s="2" t="n">
-        <v>3.629346109856249</v>
-      </c>
-      <c r="F6" s="2" t="n">
-        <v>3.643619404422672</v>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>0.75</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>1.583</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>3.629</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>3.644</t>
+        </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>GroupKFold</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C7" s="2" t="n">
-        <v>0.8500000000000001</v>
-      </c>
-      <c r="D7" s="2" t="n">
-        <v>2.648511112717022</v>
-      </c>
-      <c r="E7" s="2" t="n">
-        <v>6.415236164805004</v>
-      </c>
-      <c r="F7" s="2" t="n">
-        <v>6.068660694785058</v>
+          <t>Group KFold</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>0.85</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>2.649</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>6.415</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>6.069</t>
+        </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>GroupKFold</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="C8" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="D8" s="2" t="n">
-        <v>2.150619591856801</v>
-      </c>
-      <c r="E8" s="2" t="n">
-        <v>5.135309230426653</v>
-      </c>
-      <c r="F8" s="2" t="n">
-        <v>4.390544804831394</v>
+          <t>Group KFold</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>1.00</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>2.151</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>5.135</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>4.391</t>
+        </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>GroupKFold</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="C9" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="D9" s="2" t="n">
-        <v>2.144913684362174</v>
-      </c>
-      <c r="E9" s="2" t="n">
-        <v>5.061147978188461</v>
-      </c>
-      <c r="F9" s="2" t="n">
-        <v>4.586329881757852</v>
+          <t>Group KFold</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>1.00</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>2.145</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>5.061</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>4.586</t>
+        </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>GroupKFold</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="C10" s="2" t="n">
-        <v>0.65</v>
-      </c>
-      <c r="D10" s="2" t="n">
-        <v>3.083880251886634</v>
-      </c>
-      <c r="E10" s="2" t="n">
-        <v>6.937115739449984</v>
-      </c>
-      <c r="F10" s="2" t="n">
-        <v>7.057565513944466</v>
+          <t>Group KFold</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>0.65</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>3.084</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>6.937</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>7.058</t>
+        </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>GroupKFold</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="C11" s="2" t="n">
-        <v>0.9500000000000001</v>
-      </c>
-      <c r="D11" s="2" t="n">
-        <v>1.896178507131558</v>
-      </c>
-      <c r="E11" s="2" t="n">
-        <v>4.485176092266032</v>
-      </c>
-      <c r="F11" s="2" t="n">
-        <v>3.962177525361192</v>
+          <t>Group KFold</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>0.95</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>1.896</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>4.485</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>3.962</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -3363,7 +3975,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>GroupKFold</t>
+          <t>Group KFold</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
@@ -3378,19 +3990,19 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>-0.813 [-1.277, -0.448]</t>
+          <t>-0.813 [-1.263, -0.443]</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>+1.094 [+0.733, +1.421]</t>
+          <t>+1.094 [+0.725, +1.420]</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>GroupKFold</t>
+          <t>Group KFold</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
@@ -3405,19 +4017,19 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0.211 [-0.322, -0.123]</t>
+          <t>-0.211 [-0.319, -0.118]</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>+0.323 [+0.195, +0.457]</t>
+          <t>+0.323 [+0.185, +0.455]</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>GroupKFold</t>
+          <t>Group KFold</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
@@ -3432,19 +4044,19 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>-0.222 [-0.344, -0.120]</t>
+          <t>-0.222 [-0.352, -0.121]</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>+0.346 [+0.205, +0.490]</t>
+          <t>+0.346 [+0.209, +0.490]</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>GroupKFold</t>
+          <t>Group KFold</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
@@ -3459,19 +4071,19 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-0.372 [-0.671, -0.137]</t>
+          <t>-0.372 [-0.654, -0.139]</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>+0.552 [+0.241, +0.834]</t>
+          <t>+0.552 [+0.248, +0.812]</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>GroupKFold</t>
+          <t>Group KFold</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
@@ -3486,19 +4098,19 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>-0.011 [-0.057, +0.034]</t>
+          <t>-0.011 [-0.058, +0.034]</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>+0.018 [-0.055, +0.092]</t>
+          <t>+0.018 [-0.053, +0.094]</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>GroupKFold</t>
+          <t>Group KFold</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
@@ -3513,12 +4125,12 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-0.009 [-0.047, +0.021]</t>
+          <t>-0.009 [-0.047, +0.022]</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>+0.015 [-0.038, +0.072]</t>
+          <t>+0.015 [-0.039, +0.074]</t>
         </is>
       </c>
     </row>
@@ -3695,12 +4307,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>+0.345 [+0.091, +0.625]</t>
+          <t>+0.345 [+0.091, +0.619]</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-0.508 [-0.789, -0.156]</t>
+          <t>-0.508 [-0.785, -0.160]</t>
         </is>
       </c>
     </row>
@@ -3727,12 +4339,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>+0.008 [-0.001, +0.019]</t>
+          <t>+0.008 [-0.002, +0.019]</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-0.013 [-0.029, +0.002]</t>
+          <t>-0.013 [-0.030, +0.003]</t>
         </is>
       </c>
     </row>
@@ -3764,7 +4376,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-0.043 [-0.086, -0.004]</t>
+          <t>-0.043 [-0.087, -0.004]</t>
         </is>
       </c>
     </row>
@@ -3848,8 +4460,10 @@
           <t>2.007 (0.111)</t>
         </is>
       </c>
-      <c r="F2" s="2" t="n">
-        <v>0.017</v>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>0.017</t>
+        </is>
       </c>
     </row>
     <row r="3">
@@ -3878,8 +4492,10 @@
           <t>1.880 (0.119)</t>
         </is>
       </c>
-      <c r="F3" s="2" t="n">
-        <v>0.016</v>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>0.016</t>
+        </is>
       </c>
     </row>
     <row r="4">
@@ -3908,8 +4524,10 @@
           <t>1.797 (0.112)</t>
         </is>
       </c>
-      <c r="F4" s="2" t="n">
-        <v>0.011</v>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>0.011</t>
+        </is>
       </c>
     </row>
     <row r="5">
@@ -3938,8 +4556,10 @@
           <t>2.071 (0.090)</t>
         </is>
       </c>
-      <c r="F5" s="2" t="n">
-        <v>0.002</v>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>0.002</t>
+        </is>
       </c>
     </row>
     <row r="6">
@@ -3968,8 +4588,10 @@
           <t>1.988 (0.101)</t>
         </is>
       </c>
-      <c r="F6" s="2" t="n">
-        <v>0.008999999999999999</v>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>0.009</t>
+        </is>
       </c>
     </row>
     <row r="7">
@@ -3998,14 +4620,16 @@
           <t>1.940 (0.085)</t>
         </is>
       </c>
-      <c r="F7" s="2" t="n">
-        <v>0.003</v>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>0.003</t>
+        </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>GroupKFold</t>
+          <t>Group KFold</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
@@ -4028,14 +4652,16 @@
           <t>3.053 (0.503)</t>
         </is>
       </c>
-      <c r="F8" s="2" t="n">
-        <v>0.664</v>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>0.664</t>
+        </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>GroupKFold</t>
+          <t>Group KFold</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
@@ -4058,14 +4684,16 @@
           <t>2.392 (0.398)</t>
         </is>
       </c>
-      <c r="F9" s="2" t="n">
-        <v>0.023</v>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>0.023</t>
+        </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>GroupKFold</t>
+          <t>Group KFold</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
@@ -4088,14 +4716,16 @@
           <t>2.335 (0.345)</t>
         </is>
       </c>
-      <c r="F10" s="2" t="n">
-        <v>0.023</v>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>0.023</t>
+        </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>GroupKFold</t>
+          <t>Group KFold</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
@@ -4118,14 +4748,16 @@
           <t>2.314 (0.340)</t>
         </is>
       </c>
-      <c r="F11" s="2" t="n">
-        <v>0.005</v>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>0.005</t>
+        </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>GroupKFold</t>
+          <t>Group KFold</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
@@ -4148,14 +4780,16 @@
           <t>2.394 (0.389)</t>
         </is>
       </c>
-      <c r="F12" s="2" t="n">
-        <v>0.013</v>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>0.013</t>
+        </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>GroupKFold</t>
+          <t>Group KFold</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
@@ -4178,8 +4812,10 @@
           <t>2.334 (0.365)</t>
         </is>
       </c>
-      <c r="F13" s="2" t="n">
-        <v>0.006</v>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>0.006</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -4293,7 +4929,7 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>GroupKFold</t>
+          <t>Group KFold</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
@@ -4303,19 +4939,19 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>+0.469 [+0.212, +0.822]</t>
+          <t>+0.469 [+0.202, +0.818]</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-0.691 [-1.010, -0.365]</t>
+          <t>-0.691 [-1.007, -0.354]</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>GroupKFold</t>
+          <t>Group KFold</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
@@ -4325,19 +4961,19 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>-0.004 [-0.026, +0.021]</t>
+          <t>-0.004 [-0.026, +0.020]</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>+0.006 [-0.033, +0.042]</t>
+          <t>+0.006 [-0.033, +0.043]</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>GroupKFold</t>
+          <t>Group KFold</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
@@ -4347,12 +4983,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-0.005 [-0.028, +0.025]</t>
+          <t>-0.005 [-0.029, +0.026]</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>+0.008 [-0.040, +0.050]</t>
+          <t>+0.008 [-0.040, +0.052]</t>
         </is>
       </c>
     </row>
@@ -4482,7 +5118,7 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>GroupKFold</t>
+          <t>Group KFold</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
@@ -4507,7 +5143,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>GroupKFold</t>
+          <t>Group KFold</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
@@ -4532,7 +5168,7 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>GroupKFold</t>
+          <t>Group KFold</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
@@ -4880,13 +5516,13 @@
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
-    <col width="24" customWidth="1" min="5" max="5"/>
-    <col width="20" customWidth="1" min="6" max="6"/>
-    <col width="20" customWidth="1" min="7" max="7"/>
-    <col width="21" customWidth="1" min="8" max="8"/>
-    <col width="20" customWidth="1" min="9" max="9"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4942,29 +5578,45 @@
           <t>price (USD/call)</t>
         </is>
       </c>
-      <c r="B2" s="2" t="n">
-        <v>2879</v>
-      </c>
-      <c r="C2" s="2" t="n">
-        <v>0.0916554322746865</v>
-      </c>
-      <c r="D2" s="2" t="n">
-        <v>0.7084855408848508</v>
-      </c>
-      <c r="E2" s="2" t="n">
-        <v>1.399991600050399e-09</v>
-      </c>
-      <c r="F2" s="2" t="n">
-        <v>0.0013999916000503</v>
-      </c>
-      <c r="G2" s="2" t="n">
-        <v>0.0069999580002519</v>
-      </c>
-      <c r="H2" s="2" t="n">
-        <v>0.0279998320010079</v>
-      </c>
-      <c r="I2" s="2" t="n">
-        <v>20.99987400075599</v>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>2879</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>0.0917</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>0.7085</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>1.40e−9</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>0.0014</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>0.0070</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>0.0280</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>21.000</t>
+        </is>
       </c>
     </row>
     <row r="3">
@@ -4973,29 +5625,45 @@
           <t>ln(price)</t>
         </is>
       </c>
-      <c r="B3" s="2" t="n">
-        <v>2879</v>
-      </c>
-      <c r="C3" s="2" t="n">
-        <v>-5.423431112755735</v>
-      </c>
-      <c r="D3" s="2" t="n">
-        <v>2.808645225339028</v>
-      </c>
-      <c r="E3" s="2" t="n">
-        <v>-20.3867996003072</v>
-      </c>
-      <c r="F3" s="2" t="n">
-        <v>-6.571289042342995</v>
-      </c>
-      <c r="G3" s="2" t="n">
-        <v>-4.961851129908838</v>
-      </c>
-      <c r="H3" s="2" t="n">
-        <v>-3.575556768788937</v>
-      </c>
-      <c r="I3" s="2" t="n">
-        <v>3.044516437741423</v>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>2879</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>-5.423</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>2.809</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>-20.387</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>-6.571</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>-4.962</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>-3.576</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>3.045</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -5123,12 +5791,12 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -5160,12 +5828,12 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -5308,12 +5976,12 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -5345,12 +6013,12 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -5444,10 +6112,10 @@
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
     <col width="33" customWidth="1" min="2" max="2"/>
-    <col width="21" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
     <col width="21" customWidth="1" min="5" max="5"/>
-    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="17" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -5493,14 +6161,26 @@
           <t>Text only — Global</t>
         </is>
       </c>
-      <c r="C2" s="2" t="n">
-        <v>0.435895712512249</v>
-      </c>
-      <c r="D2" s="2" t="n">
-        <v>0.2531324018034106</v>
-      </c>
-      <c r="E2" s="2" t="inlineStr"/>
-      <c r="F2" s="2" t="inlineStr"/>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>0.436</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>0.253</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -5513,14 +6193,26 @@
           <t>KG only — Global</t>
         </is>
       </c>
-      <c r="C3" s="2" t="n">
-        <v>0.3493072330122977</v>
-      </c>
-      <c r="D3" s="2" t="n">
-        <v>-0.7030213811291111</v>
-      </c>
-      <c r="E3" s="2" t="inlineStr"/>
-      <c r="F3" s="2" t="inlineStr"/>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>0.349</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>-0.703</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -5533,14 +6225,26 @@
           <t>KG + Text — Global</t>
         </is>
       </c>
-      <c r="C4" s="2" t="n">
-        <v>0.482303338908512</v>
-      </c>
-      <c r="D4" s="2" t="n">
-        <v>-0.1674716088142577</v>
-      </c>
-      <c r="E4" s="2" t="inlineStr"/>
-      <c r="F4" s="2" t="inlineStr"/>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>0.482</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>-0.167</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -5553,14 +6257,26 @@
           <t>Text only — Local GapTrim</t>
         </is>
       </c>
-      <c r="C5" s="2" t="n">
-        <v>0.5148881382022175</v>
-      </c>
-      <c r="D5" s="2" t="n">
-        <v>0.2373275601399677</v>
-      </c>
-      <c r="E5" s="2" t="inlineStr"/>
-      <c r="F5" s="2" t="inlineStr"/>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>0.515</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>0.237</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -5573,14 +6289,26 @@
           <t>KG only — Local GapTrim</t>
         </is>
       </c>
-      <c r="C6" s="2" t="n">
-        <v>0.477001927251861</v>
-      </c>
-      <c r="D6" s="2" t="n">
-        <v>0.01353475240872681</v>
-      </c>
-      <c r="E6" s="2" t="inlineStr"/>
-      <c r="F6" s="2" t="inlineStr"/>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>0.477</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>0.014</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -5593,14 +6321,26 @@
           <t>KG + Text — Local GapTrim</t>
         </is>
       </c>
-      <c r="C7" s="2" t="n">
-        <v>0.5436253898892156</v>
-      </c>
-      <c r="D7" s="2" t="n">
-        <v>0.2370432299885344</v>
-      </c>
-      <c r="E7" s="2" t="inlineStr"/>
-      <c r="F7" s="2" t="inlineStr"/>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>0.544</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>0.237</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -5613,14 +6353,26 @@
           <t>Text only — Bayes GapTrim</t>
         </is>
       </c>
-      <c r="C8" s="2" t="n">
-        <v>0.5302391631873846</v>
-      </c>
-      <c r="D8" s="2" t="n">
-        <v>0.2740077728440838</v>
-      </c>
-      <c r="E8" s="2" t="inlineStr"/>
-      <c r="F8" s="2" t="inlineStr"/>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>0.530</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>0.274</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -5633,14 +6385,26 @@
           <t>KG only — Bayes GapTrim</t>
         </is>
       </c>
-      <c r="C9" s="2" t="n">
-        <v>0.5133538331211953</v>
-      </c>
-      <c r="D9" s="2" t="n">
-        <v>0.03726044943927329</v>
-      </c>
-      <c r="E9" s="2" t="inlineStr"/>
-      <c r="F9" s="2" t="inlineStr"/>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>0.513</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>0.037</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -5653,14 +6417,26 @@
           <t>KG + Text — Bayes GapTrim</t>
         </is>
       </c>
-      <c r="C10" s="2" t="n">
-        <v>0.5862623053541831</v>
-      </c>
-      <c r="D10" s="2" t="n">
-        <v>0.264937255049582</v>
-      </c>
-      <c r="E10" s="2" t="inlineStr"/>
-      <c r="F10" s="2" t="inlineStr"/>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>0.586</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>0.265</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -5673,14 +6449,26 @@
           <t>Global Ridge</t>
         </is>
       </c>
-      <c r="C11" s="2" t="n">
-        <v>0.482303338908512</v>
-      </c>
-      <c r="D11" s="2" t="n">
-        <v>-0.1674716088142577</v>
-      </c>
-      <c r="E11" s="2" t="inlineStr"/>
-      <c r="F11" s="2" t="inlineStr"/>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>0.482</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>-0.167</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -5693,14 +6481,26 @@
           <t>Local KNN GapTrim</t>
         </is>
       </c>
-      <c r="C12" s="2" t="n">
-        <v>0.5436253898892156</v>
-      </c>
-      <c r="D12" s="2" t="n">
-        <v>0.2370432299885344</v>
-      </c>
-      <c r="E12" s="2" t="inlineStr"/>
-      <c r="F12" s="2" t="inlineStr"/>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>0.544</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>0.237</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -5713,17 +6513,25 @@
           <t>50/50 fusion (non-Bayes)</t>
         </is>
       </c>
-      <c r="C13" s="2" t="n">
-        <v>0.5955257648331826</v>
-      </c>
-      <c r="D13" s="2" t="n">
-        <v>0.2063654365647276</v>
-      </c>
-      <c r="E13" s="2" t="n">
-        <v>0.9520543478260869</v>
-      </c>
-      <c r="F13" s="2" t="n">
-        <v>11.21359408205445</v>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>0.596</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>0.206</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>95.21%</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>11.214</t>
+        </is>
       </c>
     </row>
     <row r="14">
@@ -5737,17 +6545,25 @@
           <t>Tuned convex fusion (non-Bayes)</t>
         </is>
       </c>
-      <c r="C14" s="2" t="n">
-        <v>0.5940866109322991</v>
-      </c>
-      <c r="D14" s="2" t="n">
-        <v>0.2460148300257654</v>
-      </c>
-      <c r="E14" s="2" t="n">
-        <v>0.9253031400966183</v>
-      </c>
-      <c r="F14" s="2" t="n">
-        <v>10.42611136827199</v>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>0.594</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>0.246</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>92.53%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>10.426</t>
+        </is>
       </c>
     </row>
     <row r="15">
@@ -5761,17 +6577,25 @@
           <t>Bayes reconciliation (GapTrim)</t>
         </is>
       </c>
-      <c r="C15" s="2" t="n">
-        <v>0.5862623053541831</v>
-      </c>
-      <c r="D15" s="2" t="n">
-        <v>0.264937255049582</v>
-      </c>
-      <c r="E15" s="2" t="n">
-        <v>0.7380833333333333</v>
-      </c>
-      <c r="F15" s="2" t="n">
-        <v>4.494417875371728</v>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>0.586</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>0.265</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>73.81%</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>4.494</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -5789,7 +6613,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -5810,8 +6634,10 @@
           <t>Supplier fixed-effect share, R² = SSB/SST</t>
         </is>
       </c>
-      <c r="B2" s="2" t="n">
-        <v>0.5556954351977129</v>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>0.556</t>
+        </is>
       </c>
     </row>
     <row r="3">
@@ -5820,8 +6646,10 @@
           <t>Between-supplier sum of squares, SSB</t>
         </is>
       </c>
-      <c r="B3" s="2" t="n">
-        <v>12615.99151333621</v>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>12615.992</t>
+        </is>
       </c>
     </row>
     <row r="4">
@@ -5830,8 +6658,10 @@
           <t>Total sum of squares, SST</t>
         </is>
       </c>
-      <c r="B4" s="2" t="n">
-        <v>22703.06846923715</v>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>22703.068</t>
+        </is>
       </c>
     </row>
     <row r="5">
@@ -5840,8 +6670,10 @@
           <t>Intra-class correlation (random intercept), ICC</t>
         </is>
       </c>
-      <c r="B5" s="2" t="n">
-        <v>0.5977006425694164</v>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>0.598</t>
+        </is>
       </c>
     </row>
     <row r="6">
@@ -5850,8 +6682,10 @@
           <t>Between-supplier variance, σᵤ²</t>
         </is>
       </c>
-      <c r="B6" s="2" t="n">
-        <v>5.717788360858454</v>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>5.718</t>
+        </is>
       </c>
     </row>
     <row r="7">
@@ -5860,8 +6694,10 @@
           <t>Residual (within-supplier) variance, σₑ²</t>
         </is>
       </c>
-      <c r="B7" s="2" t="n">
-        <v>3.848519509045494</v>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>3.849</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -5880,14 +6716,14 @@
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="21" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
-    <col width="21" customWidth="1" min="5" max="5"/>
-    <col width="20" customWidth="1" min="6" max="6"/>
-    <col width="20" customWidth="1" min="7" max="7"/>
-    <col width="24" customWidth="1" min="8" max="8"/>
-    <col width="20" customWidth="1" min="9" max="9"/>
-    <col width="24" customWidth="1" min="10" max="10"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="17" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="19" customWidth="1" min="9" max="9"/>
+    <col width="17" customWidth="1" min="10" max="10"/>
     <col width="23" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
@@ -5954,32 +6790,50 @@
           <t>KFold</t>
         </is>
       </c>
-      <c r="B2" s="2" t="n">
-        <v>2879</v>
-      </c>
-      <c r="C2" s="2" t="n">
-        <v>0.08731613768162864</v>
-      </c>
-      <c r="D2" s="2" t="n">
-        <v>2.01918516398948</v>
-      </c>
-      <c r="E2" s="2" t="n">
-        <v>-0.6133236077920421</v>
-      </c>
-      <c r="F2" s="2" t="n">
-        <v>3.547824298319249</v>
-      </c>
-      <c r="G2" s="2" t="n">
-        <v>1683.224055970388</v>
-      </c>
-      <c r="H2" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I2" s="2" t="n">
-        <v>0.9584784507751465</v>
-      </c>
-      <c r="J2" s="2" t="n">
-        <v>6.209909771818899e-28</v>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>2879</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>0.087</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>2.019</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>-0.613</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>3.548</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>1683.224</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>0.000</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>0.958</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>0.000</t>
+        </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
@@ -5990,35 +6844,53 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>GroupKFold</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="n">
-        <v>2879</v>
-      </c>
-      <c r="C3" s="2" t="n">
-        <v>1.131775941740863</v>
-      </c>
-      <c r="D3" s="2" t="n">
-        <v>2.706224938446396</v>
-      </c>
-      <c r="E3" s="2" t="n">
-        <v>-0.7771841828894246</v>
-      </c>
-      <c r="F3" s="2" t="n">
-        <v>1.278805647842051</v>
-      </c>
-      <c r="G3" s="2" t="n">
-        <v>484.3797854686032</v>
-      </c>
-      <c r="H3" s="2" t="n">
-        <v>6.580607873540194e-106</v>
-      </c>
-      <c r="I3" s="2" t="n">
-        <v>0.9615216851234436</v>
-      </c>
-      <c r="J3" s="2" t="n">
-        <v>5.253283998037232e-27</v>
+          <t>Group KFold</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>2879</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>1.132</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>2.706</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>-0.777</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>1.279</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>484.380</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>0.000</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>0.962</t>
+        </is>
+      </c>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>0.000</t>
+        </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
@@ -6043,18 +6915,18 @@
     <col width="13" customWidth="1" min="1" max="1"/>
     <col width="18" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
-    <col width="20" customWidth="1" min="5" max="5"/>
-    <col width="20" customWidth="1" min="6" max="6"/>
-    <col width="20" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
     <col width="20" customWidth="1" min="8" max="8"/>
     <col width="25" customWidth="1" min="9" max="9"/>
     <col width="22" customWidth="1" min="10" max="10"/>
     <col width="21" customWidth="1" min="11" max="11"/>
     <col width="33" customWidth="1" min="12" max="12"/>
-    <col width="20" customWidth="1" min="13" max="13"/>
-    <col width="19" customWidth="1" min="14" max="14"/>
-    <col width="20" customWidth="1" min="15" max="15"/>
+    <col width="15" customWidth="1" min="13" max="13"/>
+    <col width="11" customWidth="1" min="14" max="14"/>
+    <col width="10" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -6145,44 +7017,70 @@
           <t>Mean</t>
         </is>
       </c>
-      <c r="C2" s="2" t="n">
-        <v>2879</v>
-      </c>
-      <c r="D2" s="2" t="n">
-        <v>0.914184028896589</v>
-      </c>
-      <c r="E2" s="2" t="n">
-        <v>0.9141840288965888</v>
-      </c>
-      <c r="F2" s="2" t="n">
-        <v>0.9141840288965888</v>
-      </c>
-      <c r="G2" s="2" t="n">
-        <v>0.9141840288965897</v>
-      </c>
-      <c r="H2" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I2" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J2" s="2" t="n">
-        <v>0.9772705047818913</v>
-      </c>
-      <c r="K2" s="2" t="n">
-        <v>2.147845161194535</v>
-      </c>
-      <c r="L2" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M2" s="2" t="n">
-        <v>0.8204237582493922</v>
-      </c>
-      <c r="N2" s="2" t="n">
-        <v>4.381189003612512</v>
-      </c>
-      <c r="O2" s="2" t="n">
-        <v>1.831251062090351</v>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>2879</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>0.914</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>0.914</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>0.914</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>0.914</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>0.977</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>2.148</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>0.820</t>
+        </is>
+      </c>
+      <c r="N2" s="2" t="inlineStr">
+        <is>
+          <t>4.381</t>
+        </is>
+      </c>
+      <c r="O2" s="2" t="inlineStr">
+        <is>
+          <t>1.831</t>
+        </is>
       </c>
     </row>
     <row r="3">
@@ -6196,36 +7094,54 @@
           <t>Mean | [0.8,1.0]</t>
         </is>
       </c>
-      <c r="C3" s="2" t="n">
-        <v>2879</v>
-      </c>
-      <c r="D3" s="2" t="n">
-        <v>0.914184028896589</v>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>2879</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>0.914</t>
+        </is>
       </c>
       <c r="E3" s="2" t="inlineStr"/>
       <c r="F3" s="2" t="inlineStr"/>
       <c r="G3" s="2" t="inlineStr"/>
-      <c r="H3" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I3" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J3" s="2" t="n">
-        <v>0.9772705047818913</v>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>0.977</t>
+        </is>
       </c>
       <c r="K3" s="2" t="inlineStr"/>
-      <c r="L3" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M3" s="2" t="n">
-        <v>0.8204237582493922</v>
-      </c>
-      <c r="N3" s="2" t="n">
-        <v>4.381189003612512</v>
-      </c>
-      <c r="O3" s="2" t="n">
-        <v>1.831251062090351</v>
+      <c r="L3" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="inlineStr">
+        <is>
+          <t>0.820</t>
+        </is>
+      </c>
+      <c r="N3" s="2" t="inlineStr">
+        <is>
+          <t>4.381</t>
+        </is>
+      </c>
+      <c r="O3" s="2" t="inlineStr">
+        <is>
+          <t>1.831</t>
+        </is>
       </c>
     </row>
     <row r="4">
@@ -6239,44 +7155,70 @@
           <t>Gap</t>
         </is>
       </c>
-      <c r="C4" s="2" t="n">
-        <v>2879</v>
-      </c>
-      <c r="D4" s="2" t="n">
-        <v>0.8282687627922667</v>
-      </c>
-      <c r="E4" s="2" t="n">
-        <v>0.6805692012598458</v>
-      </c>
-      <c r="F4" s="2" t="n">
-        <v>0.8949830686081588</v>
-      </c>
-      <c r="G4" s="2" t="n">
-        <v>0.9141840288965888</v>
-      </c>
-      <c r="H4" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I4" s="2" t="n">
-        <v>3.252518235498437</v>
-      </c>
-      <c r="J4" s="2" t="n">
-        <v>1.163745166188244</v>
-      </c>
-      <c r="K4" s="2" t="n">
-        <v>2.558049471125887</v>
-      </c>
-      <c r="L4" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M4" s="2" t="n">
-        <v>0.8475164987843001</v>
-      </c>
-      <c r="N4" s="2" t="n">
-        <v>4.69421418368105</v>
-      </c>
-      <c r="O4" s="2" t="n">
-        <v>1.806574450602432</v>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>2879</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>0.828</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0.681</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>0.895</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0.914</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>3.253</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>1.164</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>2.558</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>0.848</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>4.694</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>1.807</t>
+        </is>
       </c>
     </row>
     <row r="5">
@@ -6290,36 +7232,54 @@
           <t>Gap | [0.6,0.8)</t>
         </is>
       </c>
-      <c r="C5" s="2" t="n">
-        <v>826</v>
-      </c>
-      <c r="D5" s="2" t="n">
-        <v>0.6805692012598442</v>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>826</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>0.681</t>
+        </is>
       </c>
       <c r="E5" s="2" t="inlineStr"/>
       <c r="F5" s="2" t="inlineStr"/>
       <c r="G5" s="2" t="inlineStr"/>
-      <c r="H5" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I5" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J5" s="2" t="n">
-        <v>1.458291401110085</v>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>1.458</t>
+        </is>
       </c>
       <c r="K5" s="2" t="inlineStr"/>
-      <c r="L5" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M5" s="2" t="n">
-        <v>0.8837772397094431</v>
-      </c>
-      <c r="N5" s="2" t="n">
-        <v>5.222251390159139</v>
-      </c>
-      <c r="O5" s="2" t="n">
-        <v>1.85559647404553</v>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>0.884</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>5.222</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>1.856</t>
+        </is>
       </c>
     </row>
     <row r="6">
@@ -6333,36 +7293,54 @@
           <t>Gap | [0.8,1.0]</t>
         </is>
       </c>
-      <c r="C6" s="2" t="n">
-        <v>2053</v>
-      </c>
-      <c r="D6" s="2" t="n">
-        <v>0.887693915167221</v>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>2053</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>0.888</t>
+        </is>
       </c>
       <c r="E6" s="2" t="inlineStr"/>
       <c r="F6" s="2" t="inlineStr"/>
       <c r="G6" s="2" t="inlineStr"/>
-      <c r="H6" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I6" s="2" t="n">
-        <v>4.15879201169021</v>
-      </c>
-      <c r="J6" s="2" t="n">
-        <v>1.045238010783743</v>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>4.159</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>1.045</t>
+        </is>
       </c>
       <c r="K6" s="2" t="inlineStr"/>
-      <c r="L6" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M6" s="2" t="n">
-        <v>0.8329274232830005</v>
-      </c>
-      <c r="N6" s="2" t="n">
-        <v>4.481764727981633</v>
-      </c>
-      <c r="O6" s="2" t="n">
-        <v>1.786471576120707</v>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>0.833</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>4.482</t>
+        </is>
+      </c>
+      <c r="O6" s="2" t="inlineStr">
+        <is>
+          <t>1.786</t>
+        </is>
       </c>
     </row>
     <row r="7">
@@ -6376,44 +7354,70 @@
           <t>Mean</t>
         </is>
       </c>
-      <c r="C7" s="2" t="n">
-        <v>2879</v>
-      </c>
-      <c r="D7" s="2" t="n">
-        <v>0.9141840288965899</v>
-      </c>
-      <c r="E7" s="2" t="n">
-        <v>0.9141840288965902</v>
-      </c>
-      <c r="F7" s="2" t="n">
-        <v>0.9141840288965902</v>
-      </c>
-      <c r="G7" s="2" t="n">
-        <v>0.9141840288965902</v>
-      </c>
-      <c r="H7" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I7" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J7" s="2" t="n">
-        <v>1.819540931000476</v>
-      </c>
-      <c r="K7" s="2" t="n">
-        <v>3.370611622111131</v>
-      </c>
-      <c r="L7" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M7" s="2" t="n">
-        <v>0.7422716220910038</v>
-      </c>
-      <c r="N7" s="2" t="n">
-        <v>4.381189003612492</v>
-      </c>
-      <c r="O7" s="2" t="n">
-        <v>2.349626068706506</v>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>2879</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>0.914</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>0.914</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>0.914</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>0.914</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>1.820</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>3.371</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>0.742</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>4.381</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>2.350</t>
+        </is>
       </c>
     </row>
     <row r="8">
@@ -6427,36 +7431,54 @@
           <t>Mean | [0.8,1.0]</t>
         </is>
       </c>
-      <c r="C8" s="2" t="n">
-        <v>2879</v>
-      </c>
-      <c r="D8" s="2" t="n">
-        <v>0.9141840288965899</v>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>2879</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>0.914</t>
+        </is>
       </c>
       <c r="E8" s="2" t="inlineStr"/>
       <c r="F8" s="2" t="inlineStr"/>
       <c r="G8" s="2" t="inlineStr"/>
-      <c r="H8" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I8" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J8" s="2" t="n">
-        <v>1.819540931000476</v>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>1.820</t>
+        </is>
       </c>
       <c r="K8" s="2" t="inlineStr"/>
-      <c r="L8" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M8" s="2" t="n">
-        <v>0.7422716220910038</v>
-      </c>
-      <c r="N8" s="2" t="n">
-        <v>4.381189003612492</v>
-      </c>
-      <c r="O8" s="2" t="n">
-        <v>2.349626068706506</v>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>0.742</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>4.381</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>2.350</t>
+        </is>
       </c>
     </row>
     <row r="9">
@@ -6470,44 +7492,70 @@
           <t>Gap</t>
         </is>
       </c>
-      <c r="C9" s="2" t="n">
-        <v>2879</v>
-      </c>
-      <c r="D9" s="2" t="n">
-        <v>0.8830826028730238</v>
-      </c>
-      <c r="E9" s="2" t="n">
-        <v>0.9141840288965882</v>
-      </c>
-      <c r="F9" s="2" t="n">
-        <v>0.9141840288965902</v>
-      </c>
-      <c r="G9" s="2" t="n">
-        <v>0.9141840288965902</v>
-      </c>
-      <c r="H9" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I9" s="2" t="n">
-        <v>4.374782910732893</v>
-      </c>
-      <c r="J9" s="2" t="n">
-        <v>1.872359876459005</v>
-      </c>
-      <c r="K9" s="2" t="n">
-        <v>3.41783219438732</v>
-      </c>
-      <c r="L9" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M9" s="2" t="n">
-        <v>0.7381035081625564</v>
-      </c>
-      <c r="N9" s="2" t="n">
-        <v>4.494385498853468</v>
-      </c>
-      <c r="O9" s="2" t="n">
-        <v>2.369230035015818</v>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>2879</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>0.883</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>0.914</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>0.914</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>0.914</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>4.375</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>1.872</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>3.418</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>0.738</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>4.494</t>
+        </is>
+      </c>
+      <c r="O9" s="2" t="inlineStr">
+        <is>
+          <t>2.369</t>
+        </is>
       </c>
     </row>
     <row r="10">
@@ -6521,36 +7569,54 @@
           <t>Gap | [0.6,0.8)</t>
         </is>
       </c>
-      <c r="C10" s="2" t="n">
-        <v>307</v>
-      </c>
-      <c r="D10" s="2" t="n">
-        <v>0.6805692012598453</v>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>307</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>0.681</t>
+        </is>
       </c>
       <c r="E10" s="2" t="inlineStr"/>
       <c r="F10" s="2" t="inlineStr"/>
       <c r="G10" s="2" t="inlineStr"/>
-      <c r="H10" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I10" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J10" s="2" t="n">
-        <v>2.286870598714665</v>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>2.287</t>
+        </is>
       </c>
       <c r="K10" s="2" t="inlineStr"/>
-      <c r="L10" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M10" s="2" t="n">
-        <v>0.6938110749185668</v>
-      </c>
-      <c r="N10" s="2" t="n">
-        <v>5.222251390159129</v>
-      </c>
-      <c r="O10" s="2" t="n">
-        <v>2.75344684424521</v>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>0.694</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>5.222</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>2.753</t>
+        </is>
       </c>
     </row>
     <row r="11">
@@ -6564,36 +7630,54 @@
           <t>Gap | [0.8,1.0]</t>
         </is>
       </c>
-      <c r="C11" s="2" t="n">
-        <v>2572</v>
-      </c>
-      <c r="D11" s="2" t="n">
-        <v>0.9072550812148767</v>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>2572</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>0.907</t>
+        </is>
       </c>
       <c r="E11" s="2" t="inlineStr"/>
       <c r="F11" s="2" t="inlineStr"/>
       <c r="G11" s="2" t="inlineStr"/>
-      <c r="H11" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I11" s="2" t="n">
-        <v>4.777604976671851</v>
-      </c>
-      <c r="J11" s="2" t="n">
-        <v>1.822882896780744</v>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>4.778</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>1.823</t>
+        </is>
       </c>
       <c r="K11" s="2" t="inlineStr"/>
-      <c r="L11" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M11" s="2" t="n">
-        <v>0.7433903576982893</v>
-      </c>
-      <c r="N11" s="2" t="n">
-        <v>4.407505705451121</v>
-      </c>
-      <c r="O11" s="2" t="n">
-        <v>2.31912046650487</v>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>0.743</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>4.408</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>2.319</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -6612,16 +7696,16 @@
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
     <col width="25" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
-    <col width="20" customWidth="1" min="5" max="5"/>
-    <col width="20" customWidth="1" min="6" max="6"/>
-    <col width="20" customWidth="1" min="7" max="7"/>
-    <col width="20" customWidth="1" min="8" max="8"/>
-    <col width="20" customWidth="1" min="9" max="9"/>
-    <col width="20" customWidth="1" min="10" max="10"/>
-    <col width="20" customWidth="1" min="11" max="11"/>
-    <col width="20" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="4" max="4"/>
+    <col width="11" customWidth="1" min="5" max="5"/>
+    <col width="11" customWidth="1" min="6" max="6"/>
+    <col width="11" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
+    <col width="10" customWidth="1" min="11" max="11"/>
+    <col width="13" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -6697,35 +7781,55 @@
           <t>Prior (Ridge)</t>
         </is>
       </c>
-      <c r="C2" s="2" t="n">
-        <v>1.032104959110938</v>
-      </c>
-      <c r="D2" s="2" t="n">
-        <v>3.306534655393915</v>
-      </c>
-      <c r="E2" s="2" t="n">
-        <v>4.28032848371168</v>
-      </c>
-      <c r="F2" s="2" t="n">
-        <v>6.416371555379176</v>
-      </c>
-      <c r="G2" s="2" t="n">
-        <v>15.2190430428426</v>
-      </c>
-      <c r="H2" s="2" t="n">
-        <v>0.7784915707222768</v>
-      </c>
-      <c r="I2" s="2" t="n">
-        <v>7.93415909005808</v>
-      </c>
-      <c r="J2" s="2" t="n">
-        <v>30.47072122272557</v>
-      </c>
-      <c r="K2" s="2" t="n">
-        <v>376.0075077720912</v>
-      </c>
-      <c r="L2" s="2" t="n">
-        <v>4069549.230528451</v>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>1.032</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>3.307</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>4.280</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>6.416</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>15.219</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>0.778</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>7.934</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>30.471</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>376.008</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>4069549.231</t>
+        </is>
       </c>
     </row>
     <row r="3">
@@ -6739,35 +7843,55 @@
           <t>KNN (Mean)</t>
         </is>
       </c>
-      <c r="C3" s="2" t="n">
-        <v>0.6916370802658074</v>
-      </c>
-      <c r="D3" s="2" t="n">
-        <v>3.006547796899852</v>
-      </c>
-      <c r="E3" s="2" t="n">
-        <v>4.083701493517038</v>
-      </c>
-      <c r="F3" s="2" t="n">
-        <v>5.954229165696733</v>
-      </c>
-      <c r="G3" s="2" t="n">
-        <v>15.42696554995976</v>
-      </c>
-      <c r="H3" s="2" t="n">
-        <v>0.6110849857013337</v>
-      </c>
-      <c r="I3" s="2" t="n">
-        <v>5.365082611081717</v>
-      </c>
-      <c r="J3" s="2" t="n">
-        <v>22.09686028906409</v>
-      </c>
-      <c r="K3" s="2" t="n">
-        <v>238.706463701897</v>
-      </c>
-      <c r="L3" s="2" t="n">
-        <v>5010094.576174188</v>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>0.692</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>3.007</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>4.084</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>5.954</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>15.427</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>0.611</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>5.365</t>
+        </is>
+      </c>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>22.097</t>
+        </is>
+      </c>
+      <c r="K3" s="2" t="inlineStr">
+        <is>
+          <t>238.706</t>
+        </is>
+      </c>
+      <c r="L3" s="2" t="inlineStr">
+        <is>
+          <t>5010094.576</t>
+        </is>
       </c>
     </row>
     <row r="4">
@@ -6781,35 +7905,55 @@
           <t>KNN (GapTrim)</t>
         </is>
       </c>
-      <c r="C4" s="2" t="n">
-        <v>0.5349098174456148</v>
-      </c>
-      <c r="D4" s="2" t="n">
-        <v>2.997245245090341</v>
-      </c>
-      <c r="E4" s="2" t="n">
-        <v>4.211435649375467</v>
-      </c>
-      <c r="F4" s="2" t="n">
-        <v>6.305297696858554</v>
-      </c>
-      <c r="G4" s="2" t="n">
-        <v>15.42696554995976</v>
-      </c>
-      <c r="H4" s="2" t="n">
-        <v>0.500000000000003</v>
-      </c>
-      <c r="I4" s="2" t="n">
-        <v>5.034437548369449</v>
-      </c>
-      <c r="J4" s="2" t="n">
-        <v>19.00000000000075</v>
-      </c>
-      <c r="K4" s="2" t="n">
-        <v>277.8548159040668</v>
-      </c>
-      <c r="L4" s="2" t="n">
-        <v>5010094.576174188</v>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>0.535</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>2.997</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>4.211</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>6.305</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>15.427</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0.500</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>5.034</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>19.000</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>277.855</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>5010094.576</t>
+        </is>
       </c>
     </row>
     <row r="5">
@@ -6823,35 +7967,55 @@
           <t>Bayes (Mean)</t>
         </is>
       </c>
-      <c r="C5" s="2" t="n">
-        <v>0.7090324899011247</v>
-      </c>
-      <c r="D5" s="2" t="n">
-        <v>3.064847846091558</v>
-      </c>
-      <c r="E5" s="2" t="n">
-        <v>4.070924729386355</v>
-      </c>
-      <c r="F5" s="2" t="n">
-        <v>6.002260383524696</v>
-      </c>
-      <c r="G5" s="2" t="n">
-        <v>15.42904095898176</v>
-      </c>
-      <c r="H5" s="2" t="n">
-        <v>0.6147575985509999</v>
-      </c>
-      <c r="I5" s="2" t="n">
-        <v>5.703503002022128</v>
-      </c>
-      <c r="J5" s="2" t="n">
-        <v>23.12515274506432</v>
-      </c>
-      <c r="K5" s="2" t="n">
-        <v>236.0022653285299</v>
-      </c>
-      <c r="L5" s="2" t="n">
-        <v>5020503.37125152</v>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>0.709</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>3.065</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>4.071</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>6.002</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>15.429</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>0.615</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>5.704</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>23.125</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>236.002</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>5020503.371</t>
+        </is>
       </c>
     </row>
     <row r="6">
@@ -6865,35 +8029,55 @@
           <t>Bayes (GapTrim)</t>
         </is>
       </c>
-      <c r="C6" s="2" t="n">
-        <v>0.6032680114294635</v>
-      </c>
-      <c r="D6" s="2" t="n">
-        <v>2.977216631408554</v>
-      </c>
-      <c r="E6" s="2" t="n">
-        <v>3.949974569070994</v>
-      </c>
-      <c r="F6" s="2" t="n">
-        <v>6.108850302943783</v>
-      </c>
-      <c r="G6" s="2" t="n">
-        <v>15.42904095898176</v>
-      </c>
-      <c r="H6" s="2" t="n">
-        <v>0.5571010269751512</v>
-      </c>
-      <c r="I6" s="2" t="n">
-        <v>4.966249971369984</v>
-      </c>
-      <c r="J6" s="2" t="n">
-        <v>17.26404986998133</v>
-      </c>
-      <c r="K6" s="2" t="n">
-        <v>236.989455977959</v>
-      </c>
-      <c r="L6" s="2" t="n">
-        <v>5020503.37125152</v>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>0.603</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>2.977</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>3.950</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>6.109</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>15.429</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>0.557</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>4.966</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>17.264</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>236.989</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>5020503.371</t>
+        </is>
       </c>
     </row>
     <row r="7">
@@ -6907,35 +8091,55 @@
           <t>Plus Bayes (Robust Cov)</t>
         </is>
       </c>
-      <c r="C7" s="2" t="n">
-        <v>0.6748333827229942</v>
-      </c>
-      <c r="D7" s="2" t="n">
-        <v>2.960326551779895</v>
-      </c>
-      <c r="E7" s="2" t="n">
-        <v>3.8844282566634</v>
-      </c>
-      <c r="F7" s="2" t="n">
-        <v>5.929511255494771</v>
-      </c>
-      <c r="G7" s="2" t="n">
-        <v>15.40869680659453</v>
-      </c>
-      <c r="H7" s="2" t="n">
-        <v>0.5981819633778052</v>
-      </c>
-      <c r="I7" s="2" t="n">
-        <v>5.005090457159429</v>
-      </c>
-      <c r="J7" s="2" t="n">
-        <v>18.30636804053649</v>
-      </c>
-      <c r="K7" s="2" t="n">
-        <v>187.3120983436701</v>
-      </c>
-      <c r="L7" s="2" t="n">
-        <v>4919397.409962622</v>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>0.675</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>2.960</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>3.884</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>5.930</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>15.409</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0.598</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>5.005</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>18.306</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>187.312</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>4919397.410</t>
+        </is>
       </c>
     </row>
     <row r="8">
@@ -6949,35 +8153,55 @@
           <t>Stacking (Conformal)</t>
         </is>
       </c>
-      <c r="C8" s="2" t="n">
-        <v>0.751016103051841</v>
-      </c>
-      <c r="D8" s="2" t="n">
-        <v>2.979032511826315</v>
-      </c>
-      <c r="E8" s="2" t="n">
-        <v>3.826315147415198</v>
-      </c>
-      <c r="F8" s="2" t="n">
-        <v>5.824210217627466</v>
-      </c>
-      <c r="G8" s="2" t="n">
-        <v>15.32300429640118</v>
-      </c>
-      <c r="H8" s="2" t="n">
-        <v>0.6448441518630047</v>
-      </c>
-      <c r="I8" s="2" t="n">
-        <v>5.360804525419383</v>
-      </c>
-      <c r="J8" s="2" t="n">
-        <v>19.14556906148357</v>
-      </c>
-      <c r="K8" s="2" t="n">
-        <v>180.6392414327255</v>
-      </c>
-      <c r="L8" s="2" t="n">
-        <v>4515398.828031762</v>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>0.751</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>2.979</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>3.826</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>5.824</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>15.323</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>0.645</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>5.361</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>19.146</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>180.639</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>4515398.828</t>
+        </is>
       </c>
     </row>
     <row r="9">
@@ -6991,35 +8215,55 @@
           <t>Prior (Ridge)</t>
         </is>
       </c>
-      <c r="C9" s="2" t="n">
-        <v>2.275521743400138</v>
-      </c>
-      <c r="D9" s="2" t="n">
-        <v>4.534225594855245</v>
-      </c>
-      <c r="E9" s="2" t="n">
-        <v>5.505279108447705</v>
-      </c>
-      <c r="F9" s="2" t="n">
-        <v>7.371292626971195</v>
-      </c>
-      <c r="G9" s="2" t="n">
-        <v>14.13566091317341</v>
-      </c>
-      <c r="H9" s="2" t="n">
-        <v>0.9374209753073861</v>
-      </c>
-      <c r="I9" s="2" t="n">
-        <v>11.53304092503093</v>
-      </c>
-      <c r="J9" s="2" t="n">
-        <v>49.02010729623814</v>
-      </c>
-      <c r="K9" s="2" t="n">
-        <v>812.1273823813397</v>
-      </c>
-      <c r="L9" s="2" t="n">
-        <v>1377333.8382359</v>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>2.276</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>4.534</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>5.505</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>7.371</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>14.136</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>0.937</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>11.533</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>49.020</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>812.127</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>1377333.838</t>
+        </is>
       </c>
     </row>
     <row r="10">
@@ -7033,35 +8277,55 @@
           <t>KNN (Mean)</t>
         </is>
       </c>
-      <c r="C10" s="2" t="n">
-        <v>1.108839848516002</v>
-      </c>
-      <c r="D10" s="2" t="n">
-        <v>4.023574785488658</v>
-      </c>
-      <c r="E10" s="2" t="n">
-        <v>5.315957116975957</v>
-      </c>
-      <c r="F10" s="2" t="n">
-        <v>7.158639042942098</v>
-      </c>
-      <c r="G10" s="2" t="n">
-        <v>15.20762097713559</v>
-      </c>
-      <c r="H10" s="2" t="n">
-        <v>0.8143607141865278</v>
-      </c>
-      <c r="I10" s="2" t="n">
-        <v>22.02181682627971</v>
-      </c>
-      <c r="J10" s="2" t="n">
-        <v>125.4359999550642</v>
-      </c>
-      <c r="K10" s="2" t="n">
-        <v>1267.26647781823</v>
-      </c>
-      <c r="L10" s="2" t="n">
-        <v>4023331.016617178</v>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>1.109</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>4.024</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>5.316</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>7.159</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>15.208</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0.814</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>22.022</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>125.436</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>1267.266</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>4023331.017</t>
+        </is>
       </c>
     </row>
     <row r="11">
@@ -7075,35 +8339,55 @@
           <t>KNN (GapTrim)</t>
         </is>
       </c>
-      <c r="C11" s="2" t="n">
-        <v>1.149234961462754</v>
-      </c>
-      <c r="D11" s="2" t="n">
-        <v>4.171894808329657</v>
-      </c>
-      <c r="E11" s="2" t="n">
-        <v>5.521460917862115</v>
-      </c>
-      <c r="F11" s="2" t="n">
-        <v>7.174159096539891</v>
-      </c>
-      <c r="G11" s="2" t="n">
-        <v>15.20762097713559</v>
-      </c>
-      <c r="H11" s="2" t="n">
-        <v>0.8216714357672392</v>
-      </c>
-      <c r="I11" s="2" t="n">
-        <v>22.76368611629496</v>
-      </c>
-      <c r="J11" s="2" t="n">
-        <v>141.2632897938835</v>
-      </c>
-      <c r="K11" s="2" t="n">
-        <v>1267.26647781823</v>
-      </c>
-      <c r="L11" s="2" t="n">
-        <v>4023331.016617178</v>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>1.149</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>4.172</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>5.521</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>7.174</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>15.208</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>0.822</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>22.764</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>141.263</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>1267.266</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>4023331.017</t>
+        </is>
       </c>
     </row>
     <row r="12">
@@ -7117,35 +8401,55 @@
           <t>Bayes (Mean)</t>
         </is>
       </c>
-      <c r="C12" s="2" t="n">
-        <v>1.12116570787956</v>
-      </c>
-      <c r="D12" s="2" t="n">
-        <v>4.056333469419195</v>
-      </c>
-      <c r="E12" s="2" t="n">
-        <v>5.354952953231699</v>
-      </c>
-      <c r="F12" s="2" t="n">
-        <v>6.958736164488489</v>
-      </c>
-      <c r="G12" s="2" t="n">
-        <v>15.07921726875808</v>
-      </c>
-      <c r="H12" s="2" t="n">
-        <v>0.7928643753867023</v>
-      </c>
-      <c r="I12" s="2" t="n">
-        <v>20.00649531049178</v>
-      </c>
-      <c r="J12" s="2" t="n">
-        <v>124.4724031996248</v>
-      </c>
-      <c r="K12" s="2" t="n">
-        <v>1032.232530617106</v>
-      </c>
-      <c r="L12" s="2" t="n">
-        <v>3538512.454322966</v>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>1.121</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>4.056</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>5.355</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>6.959</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>15.079</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>0.793</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>20.006</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>124.472</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>1032.233</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>3538512.454</t>
+        </is>
       </c>
     </row>
     <row r="13">
@@ -7159,35 +8463,55 @@
           <t>Bayes (GapTrim)</t>
         </is>
       </c>
-      <c r="C13" s="2" t="n">
-        <v>1.166637886906707</v>
-      </c>
-      <c r="D13" s="2" t="n">
-        <v>4.113768283300627</v>
-      </c>
-      <c r="E13" s="2" t="n">
-        <v>5.355092265028542</v>
-      </c>
-      <c r="F13" s="2" t="n">
-        <v>6.946270269731198</v>
-      </c>
-      <c r="G13" s="2" t="n">
-        <v>15.07921726875808</v>
-      </c>
-      <c r="H13" s="2" t="n">
-        <v>0.7925116437189351</v>
-      </c>
-      <c r="I13" s="2" t="n">
-        <v>20.92266356357936</v>
-      </c>
-      <c r="J13" s="2" t="n">
-        <v>108.8602068553742</v>
-      </c>
-      <c r="K13" s="2" t="n">
-        <v>987.9586626903488</v>
-      </c>
-      <c r="L13" s="2" t="n">
-        <v>3538512.454322966</v>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>1.167</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>4.114</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>5.355</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>6.946</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>15.079</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0.793</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>20.923</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>108.860</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>987.959</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>3538512.454</t>
+        </is>
       </c>
     </row>
     <row r="14">
@@ -7201,35 +8525,55 @@
           <t>Plus Bayes (Robust Cov)</t>
         </is>
       </c>
-      <c r="C14" s="2" t="n">
-        <v>1.235426556654097</v>
-      </c>
-      <c r="D14" s="2" t="n">
-        <v>4.018464753942718</v>
-      </c>
-      <c r="E14" s="2" t="n">
-        <v>5.242673113122625</v>
-      </c>
-      <c r="F14" s="2" t="n">
-        <v>6.714220358851003</v>
-      </c>
-      <c r="G14" s="2" t="n">
-        <v>14.94142935072188</v>
-      </c>
-      <c r="H14" s="2" t="n">
-        <v>0.7901394888276907</v>
-      </c>
-      <c r="I14" s="2" t="n">
-        <v>18.9638980593863</v>
-      </c>
-      <c r="J14" s="2" t="n">
-        <v>106.6435928131022</v>
-      </c>
-      <c r="K14" s="2" t="n">
-        <v>740.5976621973532</v>
-      </c>
-      <c r="L14" s="2" t="n">
-        <v>3083047.230377888</v>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>1.235</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>4.018</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>5.243</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>6.714</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>14.941</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>0.790</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>18.964</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>106.644</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>740.598</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>3083047.230</t>
+        </is>
       </c>
     </row>
     <row r="15">
@@ -7243,35 +8587,55 @@
           <t>Stacking (Conformal)</t>
         </is>
       </c>
-      <c r="C15" s="2" t="n">
-        <v>1.513464566576698</v>
-      </c>
-      <c r="D15" s="2" t="n">
-        <v>4.066423897800198</v>
-      </c>
-      <c r="E15" s="2" t="n">
-        <v>5.116778615041554</v>
-      </c>
-      <c r="F15" s="2" t="n">
-        <v>6.602718145140353</v>
-      </c>
-      <c r="G15" s="2" t="n">
-        <v>14.43227679796822</v>
-      </c>
-      <c r="H15" s="2" t="n">
-        <v>0.8456137917210768</v>
-      </c>
-      <c r="I15" s="2" t="n">
-        <v>13.5084753266535</v>
-      </c>
-      <c r="J15" s="2" t="n">
-        <v>77.87009437053248</v>
-      </c>
-      <c r="K15" s="2" t="n">
-        <v>559.8745565975433</v>
-      </c>
-      <c r="L15" s="2" t="n">
-        <v>1852925.423835202</v>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>1.513</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>4.066</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>5.117</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>6.603</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>14.432</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>0.846</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>13.508</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>77.870</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>559.875</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>1852925.424</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -7292,13 +8656,13 @@
     <col width="10" customWidth="1" min="2" max="2"/>
     <col width="33" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="20" customWidth="1" min="5" max="5"/>
-    <col width="20" customWidth="1" min="6" max="6"/>
-    <col width="20" customWidth="1" min="7" max="7"/>
-    <col width="20" customWidth="1" min="8" max="8"/>
-    <col width="20" customWidth="1" min="9" max="9"/>
-    <col width="20" customWidth="1" min="10" max="10"/>
-    <col width="20" customWidth="1" min="11" max="11"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="17" customWidth="1" min="8" max="8"/>
+    <col width="17" customWidth="1" min="9" max="9"/>
+    <col width="15" customWidth="1" min="10" max="10"/>
+    <col width="15" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -7374,29 +8738,45 @@
           <t>Top25% prior-local disagreement</t>
         </is>
       </c>
-      <c r="D2" s="2" t="n">
-        <v>720</v>
-      </c>
-      <c r="E2" s="2" t="n">
-        <v>0.914184028896589</v>
-      </c>
-      <c r="F2" s="2" t="n">
-        <v>0.8315216510444741</v>
-      </c>
-      <c r="G2" s="2" t="n">
-        <v>0.8388483503310522</v>
-      </c>
-      <c r="H2" s="2" t="n">
-        <v>4.651782593895455</v>
-      </c>
-      <c r="I2" s="2" t="n">
-        <v>4.64267243062698</v>
-      </c>
-      <c r="J2" s="2" t="n">
-        <v>44.57638576059782</v>
-      </c>
-      <c r="K2" s="2" t="n">
-        <v>43.49954488820993</v>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>720.000</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>0.914</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>0.832</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>0.839</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>4.652</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>4.643</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>44.576</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>43.500</t>
+        </is>
       </c>
     </row>
     <row r="3">
@@ -7415,29 +8795,45 @@
           <t>Top10% prior-local disagreement</t>
         </is>
       </c>
-      <c r="D3" s="2" t="n">
-        <v>288</v>
-      </c>
-      <c r="E3" s="2" t="n">
-        <v>0.9141840288965892</v>
-      </c>
-      <c r="F3" s="2" t="n">
-        <v>0.8803511823235217</v>
-      </c>
-      <c r="G3" s="2" t="n">
-        <v>0.8560220240846387</v>
-      </c>
-      <c r="H3" s="2" t="n">
-        <v>5.170333577600071</v>
-      </c>
-      <c r="I3" s="2" t="n">
-        <v>4.839576437731819</v>
-      </c>
-      <c r="J3" s="2" t="n">
-        <v>56.70218341579416</v>
-      </c>
-      <c r="K3" s="2" t="n">
-        <v>50.5119378410699</v>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>288.000</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>0.914</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>0.880</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>0.856</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>5.170</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>4.840</t>
+        </is>
+      </c>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>56.702</t>
+        </is>
+      </c>
+      <c r="K3" s="2" t="inlineStr">
+        <is>
+          <t>50.512</t>
+        </is>
       </c>
     </row>
     <row r="4">
@@ -7456,29 +8852,45 @@
           <t>Top25% prior-local disagreement</t>
         </is>
       </c>
-      <c r="D4" s="2" t="n">
-        <v>720</v>
-      </c>
-      <c r="E4" s="2" t="n">
-        <v>0.799289322000408</v>
-      </c>
-      <c r="F4" s="2" t="n">
-        <v>0.5859225755550077</v>
-      </c>
-      <c r="G4" s="2" t="n">
-        <v>0.7424045691824851</v>
-      </c>
-      <c r="H4" s="2" t="n">
-        <v>5.298317366548029</v>
-      </c>
-      <c r="I4" s="2" t="n">
-        <v>4.645275455941588</v>
-      </c>
-      <c r="J4" s="2" t="n">
-        <v>44.56401108788372</v>
-      </c>
-      <c r="K4" s="2" t="n">
-        <v>30.79533711682565</v>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>720.000</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0.799</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>0.586</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0.742</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>5.298</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>4.645</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>44.564</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>30.795</t>
+        </is>
       </c>
     </row>
     <row r="5">
@@ -7497,29 +8909,45 @@
           <t>Top10% prior-local disagreement</t>
         </is>
       </c>
-      <c r="D5" s="2" t="n">
-        <v>288</v>
-      </c>
-      <c r="E5" s="2" t="n">
-        <v>0.7839622821779784</v>
-      </c>
-      <c r="F5" s="2" t="n">
-        <v>0.4869843553157628</v>
-      </c>
-      <c r="G5" s="2" t="n">
-        <v>0.6980907091233471</v>
-      </c>
-      <c r="H5" s="2" t="n">
-        <v>6.384517352059596</v>
-      </c>
-      <c r="I5" s="2" t="n">
-        <v>5.443035365820002</v>
-      </c>
-      <c r="J5" s="2" t="n">
-        <v>95.13738295109081</v>
-      </c>
-      <c r="K5" s="2" t="n">
-        <v>48.12519063502669</v>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>288.000</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>0.784</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>0.487</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>0.698</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>6.385</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>5.443</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>95.137</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>48.125</t>
+        </is>
       </c>
     </row>
     <row r="6">
@@ -7538,29 +8966,45 @@
           <t>Top25% prior-local disagreement</t>
         </is>
       </c>
-      <c r="D6" s="2" t="n">
-        <v>720</v>
-      </c>
-      <c r="E6" s="2" t="n">
-        <v>0.9141840288965895</v>
-      </c>
-      <c r="F6" s="2" t="n">
-        <v>0.9536785711480952</v>
-      </c>
-      <c r="G6" s="2" t="n">
-        <v>0.9089054063765138</v>
-      </c>
-      <c r="H6" s="2" t="n">
-        <v>6.598212670820707</v>
-      </c>
-      <c r="I6" s="2" t="n">
-        <v>6.364541125995028</v>
-      </c>
-      <c r="J6" s="2" t="n">
-        <v>614.8665212230546</v>
-      </c>
-      <c r="K6" s="2" t="n">
-        <v>524.7271016499056</v>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>720.000</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>0.914</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>0.954</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>0.909</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>6.598</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>6.365</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>614.867</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>524.727</t>
+        </is>
       </c>
     </row>
     <row r="7">
@@ -7579,29 +9023,45 @@
           <t>Top10% prior-local disagreement</t>
         </is>
       </c>
-      <c r="D7" s="2" t="n">
-        <v>288</v>
-      </c>
-      <c r="E7" s="2" t="n">
-        <v>0.9141840288965892</v>
-      </c>
-      <c r="F7" s="2" t="n">
-        <v>0.9647014574005446</v>
-      </c>
-      <c r="G7" s="2" t="n">
-        <v>0.9008669437480341</v>
-      </c>
-      <c r="H7" s="2" t="n">
-        <v>5.197515815540789</v>
-      </c>
-      <c r="I7" s="2" t="n">
-        <v>4.986271457242321</v>
-      </c>
-      <c r="J7" s="2" t="n">
-        <v>107.0635537451253</v>
-      </c>
-      <c r="K7" s="2" t="n">
-        <v>77.55422526054133</v>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>288.000</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>0.914</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>0.965</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>0.901</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>5.198</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>4.986</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>107.064</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>77.554</t>
+        </is>
       </c>
     </row>
     <row r="8">
@@ -7620,29 +9080,45 @@
           <t>Top25% prior-local disagreement</t>
         </is>
       </c>
-      <c r="D8" s="2" t="n">
-        <v>720</v>
-      </c>
-      <c r="E8" s="2" t="n">
-        <v>0.8746399529499866</v>
-      </c>
-      <c r="F8" s="2" t="n">
-        <v>2.204192487119427</v>
-      </c>
-      <c r="G8" s="2" t="n">
-        <v>0.9431005088719622</v>
-      </c>
-      <c r="H8" s="2" t="n">
-        <v>6.644688956613819</v>
-      </c>
-      <c r="I8" s="2" t="n">
-        <v>6.18852078544729</v>
-      </c>
-      <c r="J8" s="2" t="n">
-        <v>749.8325620398585</v>
-      </c>
-      <c r="K8" s="2" t="n">
-        <v>325.3609265034249</v>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>720.000</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>0.875</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>2.204</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>0.943</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>6.645</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>6.189</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>749.833</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>325.361</t>
+        </is>
       </c>
     </row>
     <row r="9">
@@ -7661,29 +9137,45 @@
           <t>Top10% prior-local disagreement</t>
         </is>
       </c>
-      <c r="D9" s="2" t="n">
-        <v>288</v>
-      </c>
-      <c r="E9" s="2" t="n">
-        <v>0.8555811902269964</v>
-      </c>
-      <c r="F9" s="2" t="n">
-        <v>2.502600050915051</v>
-      </c>
-      <c r="G9" s="2" t="n">
-        <v>0.964120892822983</v>
-      </c>
-      <c r="H9" s="2" t="n">
-        <v>6.478160418692529</v>
-      </c>
-      <c r="I9" s="2" t="n">
-        <v>5.453256370150497</v>
-      </c>
-      <c r="J9" s="2" t="n">
-        <v>493.3548387097122</v>
-      </c>
-      <c r="K9" s="2" t="n">
-        <v>102.1543453120663</v>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>288.000</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>0.856</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>2.503</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>0.964</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>6.478</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>5.453</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>493.355</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>102.154</t>
+        </is>
       </c>
     </row>
   </sheetData>
